--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-09.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G2" t="n">
         <v>2.12</v>
@@ -814,7 +814,7 @@
         <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Z2" t="n">
         <v>32</v>
@@ -826,46 +826,46 @@
         <v>12.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH2" t="n">
         <v>17</v>
       </c>
-      <c r="AG2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AI2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL2" t="n">
         <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AO2" t="n">
         <v>34</v>
       </c>
       <c r="AP2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
         <v>15</v>
@@ -874,7 +874,7 @@
         <v>23</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -886,7 +886,7 @@
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -898,7 +898,7 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
@@ -910,17 +910,17 @@
         <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.32</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
@@ -969,152 +969,152 @@
         <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.38</v>
       </c>
       <c r="G4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
         <v>2.9</v>
@@ -1163,7 +1163,7 @@
         <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
@@ -1178,25 +1178,25 @@
         <v>2.62</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R4" t="n">
         <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T4" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="U4" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
         <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X4" t="n">
         <v>32</v>
@@ -1205,7 +1205,7 @@
         <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
         <v>50</v>
@@ -1223,7 +1223,7 @@
         <v>32</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="n">
         <v>12.5</v>
@@ -1235,7 +1235,7 @@
         <v>32</v>
       </c>
       <c r="AJ4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK4" t="n">
         <v>26</v>
@@ -1262,7 +1262,7 @@
         <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
         <v>14</v>
@@ -1271,7 +1271,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
         <v>21</v>
@@ -1289,7 +1289,7 @@
         <v>23</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC4" t="n">
         <v>19</v>
@@ -1298,7 +1298,7 @@
         <v>19</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF4" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="H5" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I5" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="J5" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G6" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="I6" t="n">
         <v>2.26</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>2.98</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
         <v>3.6</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
         <v>1.74</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -2139,13 +2139,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
         <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q9" t="n">
         <v>1.16</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -2333,13 +2333,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="O10" t="n">
         <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q10" t="n">
         <v>1.22</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I12" t="n">
         <v>2.28</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>2.36</v>
       </c>
       <c r="I13" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="J13" t="n">
         <v>3.35</v>
@@ -2924,7 +2924,7 @@
         <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>2.66</v>
       </c>
       <c r="G14" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H14" t="n">
         <v>2.7</v>
@@ -3097,7 +3097,7 @@
         <v>2.82</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
         <v>3.85</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -3303,28 +3303,28 @@
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3339,7 +3339,7 @@
         <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA15" t="n">
         <v>65</v>
@@ -3363,7 +3363,7 @@
         <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI15" t="n">
         <v>65</v>
@@ -3381,13 +3381,13 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AO15" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
         <v>11.5</v>
@@ -3408,7 +3408,7 @@
         <v>12.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AX15" t="n">
         <v>13.5</v>
@@ -3426,7 +3426,7 @@
         <v>28</v>
       </c>
       <c r="BC15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD15" t="n">
         <v>36</v>
@@ -3435,14 +3435,14 @@
         <v>65</v>
       </c>
       <c r="BF15" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>1.21</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
         <v>950</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="G17" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="I17" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
         <v>3.85</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.3</v>
+        <v>2.14</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="H18" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="I18" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         <v>6.2</v>
       </c>
       <c r="H19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="J19" t="n">
         <v>4.3</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -4258,10 +4258,10 @@
         <v>3.45</v>
       </c>
       <c r="I20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J20" t="n">
         <v>3.55</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.5</v>
       </c>
       <c r="K20" t="n">
         <v>3.6</v>
@@ -4273,7 +4273,7 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
         <v>1.31</v>
@@ -4282,7 +4282,7 @@
         <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R20" t="n">
         <v>1.4</v>
@@ -4294,7 +4294,7 @@
         <v>1.74</v>
       </c>
       <c r="U20" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4318,7 +4318,7 @@
         <v>11</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD20" t="n">
         <v>14.5</v>
@@ -4336,7 +4336,7 @@
         <v>16.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ20" t="n">
         <v>30</v>
@@ -4366,16 +4366,16 @@
         <v>21</v>
       </c>
       <c r="AS20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
         <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW20" t="n">
         <v>23</v>
@@ -4390,10 +4390,10 @@
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC20" t="n">
         <v>21</v>
@@ -4402,17 +4402,17 @@
         <v>23</v>
       </c>
       <c r="BE20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG20" t="n">
         <v>22</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="G22" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="H22" t="n">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="I22" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="J22" t="n">
         <v>3.95</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="G23" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="H23" t="n">
-        <v>2.36</v>
+        <v>5.3</v>
       </c>
       <c r="I23" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K23" t="n">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -5228,10 +5228,10 @@
         <v>2.72</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
         <v>5.1</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G26" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="H26" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I26" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="J26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5446,7 +5446,7 @@
         <v>2.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -5607,19 +5607,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G27" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H27" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I27" t="n">
         <v>4.7</v>
       </c>
       <c r="J27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K27" t="n">
         <v>4.4</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="G28" t="n">
         <v>2.6</v>
       </c>
       <c r="H28" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
         <v>1.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="H29" t="n">
         <v>1.04</v>
@@ -6028,7 +6028,7 @@
         <v>2.22</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -6189,23 +6189,23 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K30" t="n">
         <v>3.9</v>
       </c>
-      <c r="H30" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K30" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q32" t="n">
         <v>1.69</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G33" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="H33" t="n">
         <v>2.84</v>
@@ -6786,7 +6786,7 @@
         <v>3.1</v>
       </c>
       <c r="K33" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -6977,10 +6977,10 @@
         <v>2.38</v>
       </c>
       <c r="J34" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K34" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -6995,10 +6995,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
         <v>2.64</v>
       </c>
       <c r="G35" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H35" t="n">
         <v>3.1</v>
@@ -7195,16 +7195,16 @@
         <v>2.3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S35" t="n">
         <v>4.5</v>
       </c>
       <c r="T35" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U35" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7213,16 +7213,16 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y35" t="n">
         <v>10.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA35" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AB35" t="n">
         <v>9.199999999999999</v>
@@ -7249,7 +7249,7 @@
         <v>60</v>
       </c>
       <c r="AJ35" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK35" t="n">
         <v>34</v>
@@ -7270,7 +7270,7 @@
         <v>9.6</v>
       </c>
       <c r="AQ35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR35" t="n">
         <v>17.5</v>
@@ -7279,7 +7279,7 @@
         <v>27</v>
       </c>
       <c r="AT35" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU35" t="n">
         <v>6.6</v>
@@ -7297,7 +7297,7 @@
         <v>11</v>
       </c>
       <c r="AZ35" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA35" t="n">
         <v>30</v>
@@ -7309,7 +7309,7 @@
         <v>20</v>
       </c>
       <c r="BD35" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="BE35" t="n">
         <v>42</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -7383,10 +7383,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G37" t="n">
         <v>3.2</v>
       </c>
       <c r="H37" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I37" t="n">
         <v>3.1</v>
       </c>
       <c r="J37" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K37" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -7577,10 +7577,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
         <v>11.5</v>
       </c>
       <c r="J38" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K38" t="n">
         <v>6.2</v>
@@ -7771,10 +7771,10 @@
         <v>1.16</v>
       </c>
       <c r="P38" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R38" t="n">
         <v>1.74</v>
@@ -7786,7 +7786,7 @@
         <v>1.86</v>
       </c>
       <c r="U38" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -7944,10 +7944,10 @@
         <v>6.2</v>
       </c>
       <c r="I39" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J39" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K39" t="n">
         <v>5.5</v>
@@ -7968,13 +7968,13 @@
         <v>3.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R39" t="n">
         <v>1.93</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T39" t="n">
         <v>1.57</v>
@@ -8001,13 +8001,13 @@
         <v>160</v>
       </c>
       <c r="AB39" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC39" t="n">
         <v>13.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AE39" t="n">
         <v>1000</v>
@@ -8019,7 +8019,7 @@
         <v>11</v>
       </c>
       <c r="AH39" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI39" t="n">
         <v>55</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -8129,13 +8129,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G40" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H40" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I40" t="n">
         <v>3.6</v>
@@ -8183,7 +8183,7 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y40" t="n">
         <v>19.5</v>
@@ -8207,7 +8207,7 @@
         <v>36</v>
       </c>
       <c r="AF40" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG40" t="n">
         <v>11.5</v>
@@ -8243,7 +8243,7 @@
         <v>16</v>
       </c>
       <c r="AR40" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS40" t="n">
         <v>30</v>
@@ -8270,7 +8270,7 @@
         <v>13</v>
       </c>
       <c r="BA40" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BB40" t="n">
         <v>18</v>
@@ -8285,14 +8285,14 @@
         <v>30</v>
       </c>
       <c r="BF40" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG40" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G41" t="n">
         <v>2.32</v>
@@ -8353,7 +8353,7 @@
         <v>1.11</v>
       </c>
       <c r="P41" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q41" t="n">
         <v>1.37</v>
@@ -8368,7 +8368,7 @@
         <v>1.38</v>
       </c>
       <c r="U41" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -8380,7 +8380,7 @@
         <v>1000</v>
       </c>
       <c r="Y41" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z41" t="n">
         <v>55</v>
@@ -8392,7 +8392,7 @@
         <v>23</v>
       </c>
       <c r="AC41" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD41" t="n">
         <v>15.5</v>
@@ -8413,7 +8413,7 @@
         <v>42</v>
       </c>
       <c r="AJ41" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK41" t="n">
         <v>20</v>
@@ -8422,7 +8422,7 @@
         <v>23</v>
       </c>
       <c r="AM41" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AN41" t="n">
         <v>7.8</v>
@@ -8431,13 +8431,13 @@
         <v>12.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ41" t="n">
         <v>24</v>
       </c>
       <c r="AR41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS41" t="n">
         <v>27</v>
@@ -8452,7 +8452,7 @@
         <v>14</v>
       </c>
       <c r="AW41" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX41" t="n">
         <v>21</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -8735,13 +8735,13 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="O43" t="n">
         <v>1.23</v>
       </c>
       <c r="P43" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Q43" t="n">
         <v>1.23</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -8929,13 +8929,13 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="O44" t="n">
         <v>1.19</v>
       </c>
       <c r="P44" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Q44" t="n">
         <v>1.19</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -9123,13 +9123,13 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="O45" t="n">
         <v>1.23</v>
       </c>
       <c r="P45" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q45" t="n">
         <v>1.23</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -9317,7 +9317,7 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="O46" t="n">
         <v>1.15</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -9684,16 +9684,16 @@
         <v>1.94</v>
       </c>
       <c r="G48" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H48" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J48" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K48" t="n">
         <v>4</v>
@@ -9714,7 +9714,7 @@
         <v>2.02</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G49" t="n">
         <v>1.66</v>
@@ -9905,10 +9905,10 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10099,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q50" t="n">
         <v>1.8</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -10263,19 +10263,19 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="G51" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="H51" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="I51" t="n">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K51" t="n">
         <v>950</v>
@@ -10293,10 +10293,10 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -10457,22 +10457,22 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="G52" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="H52" t="n">
-        <v>1.7</v>
+        <v>2.94</v>
       </c>
       <c r="I52" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J52" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="K52" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -10487,10 +10487,10 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
         <v>1.79</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R53" t="n">
         <v>1.29</v>
@@ -10771,7 +10771,7 @@
         <v>34</v>
       </c>
       <c r="AT53" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU53" t="n">
         <v>7.2</v>
@@ -10807,14 +10807,14 @@
         <v>42</v>
       </c>
       <c r="BF53" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG53" t="n">
         <v>32</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -10875,10 +10875,10 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -11427,22 +11427,22 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="G57" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H57" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="J57" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K57" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -11457,10 +11457,10 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -11621,22 +11621,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="G58" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="H58" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="I58" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="J58" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K58" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -11651,10 +11651,10 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -11815,22 +11815,22 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="G59" t="n">
         <v>4.2</v>
       </c>
       <c r="H59" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J59" t="n">
-        <v>2.84</v>
+        <v>2.24</v>
       </c>
       <c r="K59" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -11845,10 +11845,10 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -12009,22 +12009,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="G60" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="H60" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="I60" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K60" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -12039,10 +12039,10 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -12218,7 +12218,7 @@
         <v>3.2</v>
       </c>
       <c r="K61" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -12233,7 +12233,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="Q61" t="n">
         <v>2.08</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -12785,22 +12785,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="G64" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="H64" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I64" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J64" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K64" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -12815,10 +12815,10 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -12979,22 +12979,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G65" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H65" t="n">
         <v>3.9</v>
       </c>
       <c r="I65" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J65" t="n">
         <v>4</v>
       </c>
       <c r="K65" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -13009,10 +13009,10 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -13173,22 +13173,22 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="G66" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="H66" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="I66" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J66" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K66" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -13203,10 +13203,10 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -13370,16 +13370,16 @@
         <v>2.1</v>
       </c>
       <c r="G67" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H67" t="n">
         <v>3.5</v>
       </c>
       <c r="I67" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J67" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K67" t="n">
         <v>3.8</v>
@@ -13397,10 +13397,10 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -13561,7 +13561,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G68" t="n">
         <v>2.4</v>
@@ -13570,10 +13570,10 @@
         <v>3</v>
       </c>
       <c r="I68" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J68" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K68" t="n">
         <v>4.4</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
         <v>1.06</v>
       </c>
       <c r="N69" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O69" t="n">
         <v>1.27</v>
@@ -13794,10 +13794,10 @@
         <v>1.45</v>
       </c>
       <c r="S69" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T69" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U69" t="n">
         <v>2.18</v>
@@ -13866,7 +13866,7 @@
         <v>15</v>
       </c>
       <c r="AQ69" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR69" t="n">
         <v>10.5</v>
@@ -13896,10 +13896,10 @@
         <v>16</v>
       </c>
       <c r="BA69" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB69" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BC69" t="n">
         <v>29</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -13961,7 +13961,7 @@
         <v>1000</v>
       </c>
       <c r="J70" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="K70" t="n">
         <v>950</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -14534,13 +14534,13 @@
         <v>4.7</v>
       </c>
       <c r="G73" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H73" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I73" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="J73" t="n">
         <v>4.7</v>
@@ -14561,10 +14561,10 @@
         <v>1.09</v>
       </c>
       <c r="P73" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R73" t="n">
         <v>2.26</v>
@@ -14588,22 +14588,22 @@
         <v>55</v>
       </c>
       <c r="Y73" t="n">
-        <v>23</v>
+        <v>370</v>
       </c>
       <c r="Z73" t="n">
         <v>19.5</v>
       </c>
       <c r="AA73" t="n">
-        <v>24</v>
+        <v>270</v>
       </c>
       <c r="AB73" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AC73" t="n">
         <v>14</v>
       </c>
       <c r="AD73" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE73" t="n">
         <v>15</v>
@@ -14612,13 +14612,13 @@
         <v>60</v>
       </c>
       <c r="AG73" t="n">
-        <v>23</v>
+        <v>370</v>
       </c>
       <c r="AH73" t="n">
         <v>14.5</v>
       </c>
       <c r="AI73" t="n">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="AJ73" t="n">
         <v>130</v>
@@ -14633,7 +14633,7 @@
         <v>70</v>
       </c>
       <c r="AN73" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AO73" t="n">
         <v>4.6</v>
@@ -14651,16 +14651,16 @@
         <v>16</v>
       </c>
       <c r="AT73" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AU73" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AV73" t="n">
         <v>11</v>
       </c>
       <c r="AW73" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX73" t="n">
         <v>28</v>
@@ -14669,7 +14669,7 @@
         <v>20</v>
       </c>
       <c r="AZ73" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA73" t="n">
         <v>17.5</v>
@@ -14681,20 +14681,20 @@
         <v>38</v>
       </c>
       <c r="BD73" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="BE73" t="n">
         <v>22</v>
       </c>
       <c r="BF73" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG73" t="n">
         <v>4.3</v>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -14731,10 +14731,10 @@
         <v>2.12</v>
       </c>
       <c r="H74" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I74" t="n">
         <v>3.95</v>
-      </c>
-      <c r="I74" t="n">
-        <v>4.1</v>
       </c>
       <c r="J74" t="n">
         <v>3.65</v>
@@ -14758,13 +14758,13 @@
         <v>2.3</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R74" t="n">
         <v>1.51</v>
       </c>
       <c r="S74" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T74" t="n">
         <v>1.64</v>
@@ -14788,7 +14788,7 @@
         <v>34</v>
       </c>
       <c r="AA74" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB74" t="n">
         <v>13</v>
@@ -14797,7 +14797,7 @@
         <v>8.4</v>
       </c>
       <c r="AD74" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE74" t="n">
         <v>44</v>
@@ -14818,7 +14818,7 @@
         <v>24</v>
       </c>
       <c r="AK74" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AL74" t="n">
         <v>32</v>
@@ -14872,10 +14872,10 @@
         <v>21</v>
       </c>
       <c r="BC74" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD74" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE74" t="n">
         <v>32</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -14922,7 +14922,7 @@
         <v>2.1</v>
       </c>
       <c r="G75" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="H75" t="n">
         <v>3.25</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -15113,22 +15113,22 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="G76" t="n">
-        <v>1000</v>
+        <v>1.74</v>
       </c>
       <c r="H76" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="I76" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="J76" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="K76" t="n">
-        <v>950</v>
+        <v>5.9</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -15143,10 +15143,10 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>1.07</v>
+        <v>2.18</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -15307,22 +15307,22 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="G77" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="H77" t="n">
-        <v>2.66</v>
+        <v>2.98</v>
       </c>
       <c r="I77" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="J77" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="K77" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -15501,41 +15501,41 @@
         </is>
       </c>
       <c r="F78" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I78" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K78" t="n">
+        <v>950</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q78" t="n">
         <v>1.84</v>
       </c>
-      <c r="G78" t="n">
-        <v>2</v>
-      </c>
-      <c r="H78" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I78" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J78" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K78" t="n">
-        <v>4</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1.86</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -15725,7 +15725,7 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q79" t="n">
         <v>1.77</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -16086,7 +16086,7 @@
         <v>1.66</v>
       </c>
       <c r="G81" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H81" t="n">
         <v>5.6</v>
@@ -16113,10 +16113,10 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -16277,19 +16277,19 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="G82" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="H82" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="I82" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="J82" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K82" t="n">
         <v>4.2</v>
@@ -16307,10 +16307,10 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -16471,13 +16471,13 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="G83" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="H83" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I83" t="n">
         <v>5.8</v>
@@ -16486,7 +16486,7 @@
         <v>3.05</v>
       </c>
       <c r="K83" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -16501,10 +16501,10 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16698,7 @@
         <v>1.46</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G85" t="n">
         <v>8</v>
@@ -16868,7 +16868,7 @@
         <v>1.52</v>
       </c>
       <c r="I85" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="J85" t="n">
         <v>4.6</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -17056,7 +17056,7 @@
         <v>1.51</v>
       </c>
       <c r="G86" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H86" t="n">
         <v>5.9</v>
@@ -17065,7 +17065,7 @@
         <v>6.6</v>
       </c>
       <c r="J86" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K86" t="n">
         <v>5.6</v>
@@ -17083,10 +17083,10 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="Q86" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -17474,13 +17474,13 @@
         <v>2.34</v>
       </c>
       <c r="Q88" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R88" t="n">
         <v>1.54</v>
       </c>
       <c r="S88" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T88" t="n">
         <v>1.59</v>
@@ -17498,10 +17498,10 @@
         <v>21</v>
       </c>
       <c r="Y88" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z88" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA88" t="n">
         <v>46</v>
@@ -17519,7 +17519,7 @@
         <v>29</v>
       </c>
       <c r="AF88" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG88" t="n">
         <v>12.5</v>
@@ -17546,7 +17546,7 @@
         <v>16</v>
       </c>
       <c r="AO88" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AP88" t="n">
         <v>18.5</v>
@@ -17555,10 +17555,10 @@
         <v>13.5</v>
       </c>
       <c r="AR88" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS88" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AT88" t="n">
         <v>12.5</v>
@@ -17579,13 +17579,13 @@
         <v>11</v>
       </c>
       <c r="AZ88" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA88" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB88" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BC88" t="n">
         <v>21</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -17635,10 +17635,10 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G89" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H89" t="n">
         <v>5.4</v>
@@ -17647,10 +17647,10 @@
         <v>5.9</v>
       </c>
       <c r="J89" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K89" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -17668,7 +17668,7 @@
         <v>2.1</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -17829,22 +17829,22 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="G90" t="n">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="H90" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="I90" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J90" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="K90" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -17859,10 +17859,10 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -18023,22 +18023,22 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="G91" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="H91" t="n">
-        <v>2.42</v>
+        <v>2.74</v>
       </c>
       <c r="I91" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="J91" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="K91" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -18053,7 +18053,7 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q91" t="n">
         <v>1.96</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -18217,7 +18217,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="G92" t="n">
         <v>2.38</v>
@@ -18232,7 +18232,7 @@
         <v>2.86</v>
       </c>
       <c r="K92" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -18638,7 +18638,7 @@
         <v>1.55</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G95" t="n">
         <v>3.05</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-05-07 04:14:56</t>
+          <t>2026-05-07 06:34:22</t>
         </is>
       </c>
     </row>
